--- a/media/reports/finance_report_user_2.xlsx
+++ b/media/reports/finance_report_user_2.xlsx
@@ -115,8 +115,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,11 +534,11 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46190.71791251956</v>
+        <v>46191.71425456466</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>TON</t>
+          <t>NVDAB</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>1.5</v>
+        <v>160</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46189.64251221719</v>
+        <v>46190.71791251956</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>TON</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -571,27 +571,27 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46189.64239757672</v>
+        <v>46189.64251221719</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>SELL</t>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -606,59 +606,59 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>46189.63935303379</v>
+        <v>46189.64239757672</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>60000</v>
+        <v>1</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>60000</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46189.61365832893</v>
+        <v>46189.63935303379</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SOL</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>BUY</t>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1</v>
+        <v>60000</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>1</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
-        <v>46189.56804701465</v>
+        <v>46189.61365832893</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>TON</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -678,11 +678,11 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46188.54464655939</v>
+        <v>46189.56804701465</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>TON</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -702,11 +702,11 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
-        <v>46188.49977222527</v>
+        <v>46188.54464655939</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -715,36 +715,60 @@
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1650</v>
+        <v>1</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>3300</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
+        <v>46188.49977222527</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
         <v>46188.49964566016</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="7" t="n">
+      <c r="D13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="12" t="n">
         <v>66000</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F13" s="12" t="n">
         <v>66000</v>
       </c>
     </row>
